--- a/exports/ZYDUSLIFE_full_report.xlsx
+++ b/exports/ZYDUSLIFE_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q66"/>
+  <dimension ref="A1:U66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>3.84</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44578.55208333334</v>
+        <v>44579.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>438.6</v>
+        <v>428.05</v>
       </c>
       <c r="I2" t="n">
         <v>435.4269</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.88</v>
+        <v>-5.21</v>
       </c>
       <c r="L2" t="n">
-        <v>3.23</v>
+        <v>6.05</v>
       </c>
       <c r="M2" t="n">
         <v>0.1</v>
       </c>
       <c r="N2" t="n">
-        <v>1.7</v>
+        <v>3.72</v>
       </c>
       <c r="O2" t="n">
         <v>0.74</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>5.24</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44589.55208333334</v>
+        <v>44592.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>396.35</v>
+        <v>407.35</v>
       </c>
       <c r="I3" t="n">
         <v>407.2121554495845</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K3" t="n">
-        <v>7.41</v>
+        <v>4.84</v>
       </c>
       <c r="L3" t="n">
         <v>2.67</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09</v>
+        <v>1.92</v>
       </c>
       <c r="N3" t="n">
         <v>2.92</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>7.47</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44603.55208333334</v>
+        <v>44606.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>391.35</v>
+        <v>387.6</v>
       </c>
       <c r="I4" t="n">
         <v>390.8997257738779</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.93</v>
+        <v>-4.85</v>
       </c>
       <c r="L4" t="n">
-        <v>4.12</v>
+        <v>6.16</v>
       </c>
       <c r="M4" t="n">
-        <v>0.29</v>
+        <v>1.12</v>
       </c>
       <c r="N4" t="n">
         <v>3.36</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>5.26</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44629.55208333334</v>
+        <v>44630.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>358.95</v>
+        <v>364.75</v>
       </c>
       <c r="I5" t="n">
         <v>363.566618794324</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>7.39</v>
+        <v>5.9</v>
       </c>
       <c r="L5" t="n">
         <v>3.19</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>7.37</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44648.38541666666</v>
+        <v>44648.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>354.95</v>
+        <v>351.55</v>
       </c>
       <c r="I6" t="n">
         <v>353.9165937403774</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.69</v>
+        <v>-3.62</v>
       </c>
       <c r="L6" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="M6" t="n">
         <v>0.79</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>6.25</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44655.55208333334</v>
+        <v>44656.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>363.3</v>
+        <v>368</v>
       </c>
       <c r="I7" t="n">
         <v>366.5463698263184</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.34</v>
+        <v>-4.68</v>
       </c>
       <c r="L7" t="n">
-        <v>4.08</v>
+        <v>5.19</v>
       </c>
       <c r="M7" t="n">
         <v>0.98</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>5.16</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44670.38541666666</v>
+        <v>44670.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>361.8</v>
+        <v>354.4</v>
       </c>
       <c r="I8" t="n">
         <v>354.9272993460379</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.68</v>
+        <v>-3.7</v>
       </c>
       <c r="L8" t="n">
         <v>5.03</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>7.09</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44698.38541666666</v>
+        <v>44698.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>348.15</v>
+        <v>349</v>
       </c>
       <c r="I9" t="n">
         <v>348.6142038918785</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>27.83333333333333</v>
+        <v>28</v>
       </c>
       <c r="K9" t="n">
-        <v>1.76</v>
+        <v>1.52</v>
       </c>
       <c r="L9" t="n">
         <v>2.74</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>6.01</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44718.55208333334</v>
+        <v>44719.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>364.5</v>
+        <v>357.45</v>
       </c>
       <c r="I10" t="n">
         <v>359.5315454010135</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>4.44</v>
+        <v>2.42</v>
       </c>
       <c r="L10" t="n">
         <v>4.11</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>5.96</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44735.55208333334</v>
+        <v>44736.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>346</v>
+        <v>351.6</v>
       </c>
       <c r="I11" t="n">
         <v>350.2751654742796</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K11" t="n">
-        <v>3.2</v>
+        <v>1.64</v>
       </c>
       <c r="L11" t="n">
         <v>2.11</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>5.52</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44763.55208333334</v>
+        <v>44764.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>354.8</v>
+        <v>351.3</v>
       </c>
       <c r="I12" t="n">
         <v>354.3897967572582</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K12" t="n">
-        <v>0.91</v>
+        <v>-0.09</v>
       </c>
       <c r="L12" t="n">
         <v>1.48</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>5.12</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44777.38541666666</v>
+        <v>44777.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>354.3</v>
+        <v>365.45</v>
       </c>
       <c r="I13" t="n">
         <v>357.5791260491228</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.85</v>
+        <v>-4.03</v>
       </c>
       <c r="L13" t="n">
-        <v>1.34</v>
+        <v>4.16</v>
       </c>
       <c r="M13" t="n">
         <v>0.42</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,25 +1385,25 @@
         <v>6.35</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44799.55208333334</v>
+        <v>44802.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>382.75</v>
+        <v>378.65</v>
       </c>
       <c r="I14" t="n">
         <v>379.2332339053955</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>22</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>4.73</v>
+        <v>3.61</v>
       </c>
       <c r="L14" t="n">
         <v>3.24</v>
       </c>
       <c r="M14" t="n">
-        <v>0.53</v>
+        <v>2.05</v>
       </c>
       <c r="N14" t="n">
         <v>2.39</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>4.37</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44832.55208333334</v>
+        <v>44833.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>368.15</v>
+        <v>380.2</v>
       </c>
       <c r="I15" t="n">
         <v>375.1388251622117</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K15" t="n">
-        <v>2.77</v>
+        <v>-0.41</v>
       </c>
       <c r="L15" t="n">
         <v>1.62</v>
@@ -1296,7 +1475,7 @@
         <v>0.84</v>
       </c>
       <c r="N15" t="n">
-        <v>3.34</v>
+        <v>3.9</v>
       </c>
       <c r="O15" t="n">
         <v>-1.21</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>7.02</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44876.38541666666</v>
+        <v>44876.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>432.65</v>
+        <v>427.9</v>
       </c>
       <c r="I16" t="n">
         <v>430.7638585312882</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>43</v>
+        <v>43.16666666666666</v>
       </c>
       <c r="K16" t="n">
-        <v>13.8</v>
+        <v>12.55</v>
       </c>
       <c r="L16" t="n">
         <v>2.68</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,25 +1592,25 @@
         <v>7.31</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44895.55208333334</v>
+        <v>44896.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>408.7</v>
+        <v>412.6</v>
       </c>
       <c r="I17" t="n">
         <v>411.5311010148514</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>4.49</v>
+        <v>3.58</v>
       </c>
       <c r="L17" t="n">
         <v>1.22</v>
       </c>
       <c r="M17" t="n">
-        <v>0.58</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
         <v>2.17</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>4.21</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44942.55208333334</v>
+        <v>44943.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>438.05</v>
+        <v>431</v>
       </c>
       <c r="I18" t="n">
         <v>434.2705719824322</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K18" t="n">
-        <v>6.17</v>
+        <v>4.46</v>
       </c>
       <c r="L18" t="n">
         <v>2.28</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>5.86</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44960.55208333334</v>
+        <v>44963.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>434.75</v>
+        <v>470</v>
       </c>
       <c r="I19" t="n">
         <v>446.6838172291582</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.87</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>3.68</v>
+        <v>10.49</v>
       </c>
       <c r="M19" t="n">
-        <v>1.24</v>
+        <v>3.97</v>
       </c>
       <c r="N19" t="n">
-        <v>2.78</v>
+        <v>7.89</v>
       </c>
       <c r="O19" t="n">
         <v>-1.5</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45064.55208333334</v>
+        <v>45065.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>507.95</v>
+        <v>493.85</v>
       </c>
       <c r="I20" t="n">
         <v>506.4432548063368</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>101.1666666666667</v>
+        <v>102</v>
       </c>
       <c r="K20" t="n">
-        <v>8.07</v>
+        <v>5.07</v>
       </c>
       <c r="L20" t="n">
         <v>4.68</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>7.43</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45090.55208333334</v>
+        <v>45091.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>518</v>
+        <v>527.4</v>
       </c>
       <c r="I21" t="n">
         <v>520.6226108512554</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.89</v>
+        <v>-6.79</v>
       </c>
       <c r="L21" t="n">
-        <v>5.98</v>
+        <v>7.61</v>
       </c>
       <c r="M21" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="N21" t="n">
-        <v>2.23</v>
+        <v>2.92</v>
       </c>
       <c r="O21" t="n">
         <v>-2.14</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4.92</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45163.38541666666</v>
+        <v>45163.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>633.35</v>
+        <v>628.5</v>
       </c>
       <c r="I22" t="n">
         <v>633.1372920366415</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>72</v>
+        <v>72.16666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>20.09</v>
+        <v>19.17</v>
       </c>
       <c r="L22" t="n">
         <v>2.24</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>4.97</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45182.38541666666</v>
+        <v>45182.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>638.25</v>
+        <v>643.2</v>
       </c>
       <c r="I23" t="n">
         <v>641.1601619312438</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>18.83333333333333</v>
+        <v>19</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.55</v>
+        <v>-2.34</v>
       </c>
       <c r="L23" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="M23" t="n">
         <v>0.59</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>4.44</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45189.55208333334</v>
+        <v>45190.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>626.15</v>
+        <v>619.4</v>
       </c>
       <c r="I24" t="n">
         <v>623.8612842160198</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.65</v>
+        <v>-3.7</v>
       </c>
       <c r="L24" t="n">
-        <v>3.05</v>
+        <v>4.03</v>
       </c>
       <c r="M24" t="n">
         <v>0.33</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>6.02</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45237.38541666666</v>
+        <v>45237.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>594.8</v>
+        <v>598.8</v>
       </c>
       <c r="I25" t="n">
         <v>595.0751615499431</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>47</v>
+        <v>47.16666666666666</v>
       </c>
       <c r="K25" t="n">
-        <v>3.97</v>
+        <v>3.33</v>
       </c>
       <c r="L25" t="n">
         <v>2.57</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>4.39</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45394.55208333334</v>
+        <v>45397.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>965</v>
+        <v>941.2</v>
       </c>
       <c r="I26" t="n">
         <v>959.9934026149494</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>157</v>
+        <v>159.8333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>61.16</v>
+        <v>57.18</v>
       </c>
       <c r="L26" t="n">
         <v>0.99</v>
       </c>
       <c r="M26" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="N26" t="n">
         <v>3.51</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>211</v>
+        <v>212</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>6.19</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45414.38541666666</v>
+        <v>45414.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>968.5</v>
+        <v>987.9</v>
       </c>
       <c r="I27" t="n">
         <v>975.2647756872107</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.9</v>
+        <v>-4.96</v>
       </c>
       <c r="L27" t="n">
-        <v>5.18</v>
+        <v>5.4</v>
       </c>
       <c r="M27" t="n">
         <v>1.21</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>6.85</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45439.55208333334</v>
+        <v>45440.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1062</v>
+        <v>1043.2</v>
       </c>
       <c r="I28" t="n">
         <v>1051.113166589333</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>25</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>7.5</v>
+        <v>5.6</v>
       </c>
       <c r="L28" t="n">
         <v>2.32</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>8.5</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45450.55208333334</v>
+        <v>45453.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1059.2</v>
+        <v>1079</v>
       </c>
       <c r="I29" t="n">
         <v>1071.691692978661</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.53</v>
+        <v>-3.43</v>
       </c>
       <c r="L29" t="n">
-        <v>2.35</v>
+        <v>4.49</v>
       </c>
       <c r="M29" t="n">
         <v>4.5</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>8.18</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45516.55208333334</v>
+        <v>45517.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1253</v>
+        <v>1184.45</v>
       </c>
       <c r="I30" t="n">
         <v>1226.289235233646</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>63.16666666666666</v>
+        <v>64</v>
       </c>
       <c r="K30" t="n">
-        <v>16.13</v>
+        <v>9.77</v>
       </c>
       <c r="L30" t="n">
         <v>2.69</v>
@@ -2151,7 +2510,7 @@
         <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.76</v>
+        <v>5.82</v>
       </c>
       <c r="O30" t="n">
         <v>2.5</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>11.77</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45632.38541666666</v>
+        <v>45632.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>983.05</v>
+        <v>994.7</v>
       </c>
       <c r="I31" t="n">
         <v>985.6139903095619</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>115</v>
+        <v>115.1666666666667</v>
       </c>
       <c r="K31" t="n">
-        <v>17</v>
+        <v>16.02</v>
       </c>
       <c r="L31" t="n">
         <v>6.21</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>158</v>
+        <v>159</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>4.26</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45650.55208333334</v>
+        <v>45652.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>964.95</v>
+        <v>956.55</v>
       </c>
       <c r="I32" t="n">
         <v>958.4533172394683</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>18</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>-2.99</v>
+        <v>-3.84</v>
       </c>
       <c r="L32" t="n">
-        <v>3.99</v>
+        <v>4.18</v>
       </c>
       <c r="M32" t="n">
         <v>1.11</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>4.56</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45663.55208333334</v>
+        <v>45664.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>963</v>
+        <v>1001.25</v>
       </c>
       <c r="I33" t="n">
         <v>994.3755849313625</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.67</v>
+        <v>-4.67</v>
       </c>
       <c r="L33" t="n">
-        <v>4.27</v>
+        <v>6.01</v>
       </c>
       <c r="M33" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="N33" t="n">
-        <v>1.9</v>
+        <v>4.05</v>
       </c>
       <c r="O33" t="n">
         <v>-0.57</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>5.96</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45681.55208333334</v>
+        <v>45684.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>959.3</v>
+        <v>933.4</v>
       </c>
       <c r="I34" t="n">
         <v>955.2317928763146</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K34" t="n">
-        <v>-4.19</v>
+        <v>-6.78</v>
       </c>
       <c r="L34" t="n">
-        <v>4.62</v>
+        <v>7.11</v>
       </c>
       <c r="M34" t="n">
         <v>1.38</v>
       </c>
       <c r="N34" t="n">
-        <v>3.08</v>
+        <v>4.31</v>
       </c>
       <c r="O34" t="n">
         <v>4.05</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,25 +2834,25 @@
         <v>6.67</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45687.55208333334</v>
+        <v>45688.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>952.4</v>
+        <v>968.7</v>
       </c>
       <c r="I35" t="n">
         <v>965.6636368522389</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.04</v>
+        <v>-3.78</v>
       </c>
       <c r="L35" t="n">
-        <v>2.52</v>
+        <v>4.25</v>
       </c>
       <c r="M35" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="N35" t="n">
         <v>2.53</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>6.31</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>965.45</v>
+        <v>938.5</v>
       </c>
       <c r="I36" t="n">
         <v>943.3152016520463</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.34</v>
+        <v>-3.12</v>
       </c>
       <c r="L36" t="n">
-        <v>2.45</v>
+        <v>3.17</v>
       </c>
       <c r="M36" t="n">
         <v>0.88</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>8.41</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45735.55208333334</v>
+        <v>45736.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>910.3</v>
+        <v>920.5</v>
       </c>
       <c r="I37" t="n">
         <v>917.9161376257663</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K37" t="n">
-        <v>3</v>
+        <v>1.92</v>
       </c>
       <c r="L37" t="n">
         <v>2.87</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>4.99</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45743.38541666666</v>
+        <v>45743.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>891.6</v>
+        <v>888.25</v>
       </c>
       <c r="I38" t="n">
         <v>888.3504378310543</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.14</v>
+        <v>-3.5</v>
       </c>
       <c r="L38" t="n">
         <v>4.2</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>5.03</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45789.55208333334</v>
+        <v>45790.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>885.3</v>
+        <v>900</v>
       </c>
       <c r="I39" t="n">
         <v>898.6964476902392</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>46</v>
+        <v>46.83333333333334</v>
       </c>
       <c r="K39" t="n">
-        <v>0.33</v>
+        <v>-1.32</v>
       </c>
       <c r="L39" t="n">
         <v>6.91</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>5.42</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45826.55208333334</v>
+        <v>45827.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>957</v>
+        <v>950.35</v>
       </c>
       <c r="I40" t="n">
         <v>953.3872376786705</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K40" t="n">
-        <v>6.33</v>
+        <v>5.59</v>
       </c>
       <c r="L40" t="n">
         <v>3.82</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>4.17</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45834.55208333334</v>
+        <v>45835.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>979.95</v>
+        <v>985</v>
       </c>
       <c r="I41" t="n">
         <v>983.9427843678116</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.11</v>
+        <v>-3.65</v>
       </c>
       <c r="L41" t="n">
-        <v>3.49</v>
+        <v>4.06</v>
       </c>
       <c r="M41" t="n">
         <v>0.95</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,25 +3317,25 @@
         <v>3.09</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45846.55208333334</v>
+        <v>45847.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>982.9</v>
+        <v>971.6</v>
       </c>
       <c r="I42" t="n">
         <v>972.8652674922311</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.21</v>
+        <v>-1.36</v>
       </c>
       <c r="L42" t="n">
         <v>1.93</v>
       </c>
       <c r="M42" t="n">
-        <v>0.29</v>
+        <v>0.97</v>
       </c>
       <c r="N42" t="n">
         <v>1.32</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>4.64</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45866.55208333334</v>
+        <v>45867.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>978</v>
+        <v>994.25</v>
       </c>
       <c r="I43" t="n">
         <v>992.8919976918645</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.66</v>
+        <v>-2.33</v>
       </c>
       <c r="L43" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="M43" t="n">
         <v>1.09</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>4.18</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45869.55208333334</v>
+        <v>45870.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>964</v>
+        <v>948.85</v>
       </c>
       <c r="I44" t="n">
         <v>960.1714417335504</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.04</v>
+        <v>-4.57</v>
       </c>
       <c r="L44" t="n">
-        <v>3.33</v>
+        <v>4.75</v>
       </c>
       <c r="M44" t="n">
         <v>1.96</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>5.57</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45881.55208333334</v>
+        <v>45882.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>955</v>
+        <v>989.15</v>
       </c>
       <c r="I45" t="n">
         <v>972.6026121286563</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.65</v>
+        <v>-4.25</v>
       </c>
       <c r="L45" t="n">
-        <v>2.31</v>
+        <v>4.86</v>
       </c>
       <c r="M45" t="n">
         <v>0.72</v>
       </c>
       <c r="N45" t="n">
-        <v>2.23</v>
+        <v>3.29</v>
       </c>
       <c r="O45" t="n">
         <v>-1.46</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.07</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45895.55208333334</v>
+        <v>45897.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>985.5</v>
+        <v>976.65</v>
       </c>
       <c r="I46" t="n">
         <v>979.0058070004188</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.37</v>
+        <v>-1.26</v>
       </c>
       <c r="L46" t="n">
         <v>5.12</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>5.62</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45908.55208333334</v>
+        <v>45909.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1010.2</v>
+        <v>1027.5</v>
       </c>
       <c r="I47" t="n">
         <v>1026.641112527025</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.44</v>
+        <v>-5.21</v>
       </c>
       <c r="L47" t="n">
         <v>6.39</v>
@@ -3120,7 +3683,7 @@
         <v>1.12</v>
       </c>
       <c r="N47" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="O47" t="n">
         <v>-0.86</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>5.27</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1019.3</v>
+        <v>984.7</v>
       </c>
       <c r="I48" t="n">
         <v>1010.559888883631</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.8</v>
+        <v>-4.17</v>
       </c>
       <c r="L48" t="n">
-        <v>1.78</v>
+        <v>4.82</v>
       </c>
       <c r="M48" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.27</v>
       </c>
       <c r="N48" t="n">
-        <v>1.48</v>
+        <v>4.35</v>
       </c>
       <c r="O48" t="n">
         <v>2.8</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>5.67</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46027.55208333334</v>
+        <v>46028.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>922.4</v>
+        <v>928.65</v>
       </c>
       <c r="I49" t="n">
         <v>925.2509297263025</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>101.1666666666667</v>
+        <v>102</v>
       </c>
       <c r="K49" t="n">
-        <v>6.33</v>
+        <v>5.69</v>
       </c>
       <c r="L49" t="n">
         <v>3.3</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>135</v>
+        <v>136</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>5</v>
+      </c>
+      <c r="U49" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>3.33</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46030.55208333334</v>
+        <v>46031.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>908</v>
+        <v>896.85</v>
       </c>
       <c r="I50" t="n">
         <v>903.5485095548346</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.22</v>
+        <v>-3.42</v>
       </c>
       <c r="L50" t="n">
-        <v>2.49</v>
+        <v>3.73</v>
       </c>
       <c r="M50" t="n">
         <v>0.32</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>4.59</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46056.38541666666</v>
+        <v>46056.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>896.25</v>
+        <v>903.4</v>
       </c>
       <c r="I51" t="n">
         <v>900.5962838198241</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K51" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.73</v>
       </c>
       <c r="L51" t="n">
         <v>2.23</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>5</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>922.85</v>
+        <v>899.6</v>
       </c>
       <c r="I52" t="n">
         <v>900.8697127373579</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>24</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>2.15</v>
+        <v>-0.42</v>
       </c>
       <c r="L52" t="n">
         <v>2.37</v>
       </c>
       <c r="M52" t="n">
-        <v>0.39</v>
+        <v>3.16</v>
       </c>
       <c r="N52" t="n">
         <v>3.8</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>5.11</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46120.55208333334</v>
+        <v>46121.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>892.45</v>
+        <v>905.9</v>
       </c>
       <c r="I53" t="n">
         <v>902.9681472483304</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K53" t="n">
-        <v>0.79</v>
+        <v>-0.7</v>
       </c>
       <c r="L53" t="n">
         <v>4.06</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.23</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46141.55208333334</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>912.05</v>
+        <v>898.5</v>
       </c>
       <c r="I54" t="n">
         <v>907.9936417308493</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K54" t="n">
-        <v>0.68</v>
+        <v>-0.82</v>
       </c>
       <c r="L54" t="n">
         <v>1.92</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>6.1</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46150.55208333334</v>
+        <v>46153.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>939</v>
+        <v>945.35</v>
       </c>
       <c r="I55" t="n">
         <v>942.5081176333017</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K55" t="n">
-        <v>-4.51</v>
+        <v>-5.21</v>
       </c>
       <c r="L55" t="n">
         <v>6.07</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.14</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46189.55208333334</v>
+        <v>46190.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1079.8</v>
+        <v>1057.2</v>
       </c>
       <c r="I56" t="n">
         <v>1059.916132504006</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K56" t="n">
-        <v>14.22</v>
+        <v>11.83</v>
       </c>
       <c r="L56" t="n">
         <v>2.14</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>5.46</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46195.55208333334</v>
+        <v>46196.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1085.5</v>
+        <v>1109</v>
       </c>
       <c r="I57" t="n">
         <v>1104.909196093345</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.68</v>
+        <v>-4.9</v>
       </c>
       <c r="L57" t="n">
-        <v>2.93</v>
+        <v>6.37</v>
       </c>
       <c r="M57" t="n">
-        <v>0.04</v>
+        <v>0.78</v>
       </c>
       <c r="N57" t="n">
-        <v>1.24</v>
+        <v>2.35</v>
       </c>
       <c r="O57" t="n">
         <v>-1.56</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>4.88</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46227.55208333334</v>
+        <v>46230.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1109.8</v>
+        <v>1107.2</v>
       </c>
       <c r="I58" t="n">
         <v>1108.354422081524</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K58" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="L58" t="n">
         <v>1.96</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>5.22</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46244.55208333334</v>
+        <v>46245.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1115</v>
+        <v>1157.6</v>
       </c>
       <c r="I59" t="n">
         <v>1143.14940608965</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.7</v>
+        <v>-4.55</v>
       </c>
       <c r="L59" t="n">
-        <v>2.59</v>
+        <v>5.11</v>
       </c>
       <c r="M59" t="n">
         <v>0.89</v>
       </c>
       <c r="N59" t="n">
-        <v>1.81</v>
+        <v>7.09</v>
       </c>
       <c r="O59" t="n">
         <v>-0.16</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,25 +4559,25 @@
         <v>5.83</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46251.55208333334</v>
+        <v>46252.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1137</v>
+        <v>1123.9</v>
       </c>
       <c r="I60" t="n">
         <v>1123.937317076882</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.78</v>
+        <v>-2.91</v>
       </c>
       <c r="L60" t="n">
         <v>3.46</v>
       </c>
       <c r="M60" t="n">
-        <v>0.34</v>
+        <v>0.45</v>
       </c>
       <c r="N60" t="n">
         <v>3</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>6.75</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46260.55208333334</v>
+        <v>46261.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1149.5</v>
+        <v>1166.2</v>
       </c>
       <c r="I61" t="n">
         <v>1152.055481139082</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.28</v>
+        <v>-3.76</v>
       </c>
       <c r="L61" t="n">
-        <v>2.37</v>
+        <v>5.26</v>
       </c>
       <c r="M61" t="n">
-        <v>0.63</v>
+        <v>0.91</v>
       </c>
       <c r="N61" t="n">
-        <v>2.25</v>
+        <v>3.41</v>
       </c>
       <c r="O61" t="n">
         <v>-1.83</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>5.44</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46269.38541666666</v>
+        <v>46269.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>1131.8</v>
+        <v>1123</v>
       </c>
       <c r="I62" t="n">
         <v>1123.958938297965</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.95</v>
+        <v>-3.7</v>
       </c>
       <c r="L62" t="n">
-        <v>3.52</v>
+        <v>3.7</v>
       </c>
       <c r="M62" t="n">
         <v>-0</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,25 +4766,25 @@
         <v>5.35</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46282.55208333334</v>
+        <v>46283.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1136</v>
+        <v>1154.4</v>
       </c>
       <c r="I63" t="n">
         <v>1154.397936140481</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.16</v>
+        <v>-2.8</v>
       </c>
       <c r="L63" t="n">
         <v>3.98</v>
       </c>
       <c r="M63" t="n">
-        <v>0.82</v>
+        <v>1.29</v>
       </c>
       <c r="N63" t="n">
         <v>3.02</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>5.05</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46295.38541666666</v>
+        <v>46295.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>1165.2</v>
+        <v>1163</v>
       </c>
       <c r="I64" t="n">
         <v>1164.901370988075</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="L64" t="n">
         <v>0.58</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>5.31</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46321.55208333334</v>
+        <v>46322.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="I65" t="n">
         <v>1164.15300505497</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K65" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.52</v>
       </c>
       <c r="L65" t="n">
-        <v>0.38</v>
+        <v>1.55</v>
       </c>
       <c r="M65" t="n">
         <v>0.8100000000000001</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4206,6 +4997,12 @@
       <c r="Q66" t="n">
         <v>2</v>
       </c>
+      <c r="R66" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6308,7 +7105,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.3</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="6">
@@ -6318,7 +7115,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.6</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="7">
@@ -6328,7 +7125,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>157</v>
+        <v>159.8</v>
       </c>
     </row>
     <row r="8">
@@ -6338,7 +7135,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -6348,7 +7145,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28.4</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="10">
@@ -6358,7 +7155,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>46.8</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="11">
@@ -6398,7 +7195,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.39</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="15">
@@ -6408,7 +7205,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.11</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="16">
@@ -6418,7 +7215,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.67</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="17">
@@ -6428,7 +7225,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>61.16</v>
+        <v>57.18</v>
       </c>
     </row>
     <row r="18">
@@ -6438,7 +7235,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46.9</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="19">
@@ -6448,7 +7245,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.14</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="20">
@@ -6458,7 +7255,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.8</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="21">
@@ -6468,7 +7265,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6.91</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="22">
@@ -6478,7 +7275,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -6488,7 +7285,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -6498,7 +7295,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.16</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="25">
@@ -6518,7 +7315,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.67</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="27">
@@ -6528,7 +7325,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.42</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="28">
@@ -6538,7 +7335,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
